--- a/artfynd/A 43407-2020 artfynd.xlsx
+++ b/artfynd/A 43407-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43407-2020 artfynd.xlsx
+++ b/artfynd/A 43407-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2460,6 +2460,130 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>92068858</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83001</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>V Sunnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>443582</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6577540</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kristinehamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ölme</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Nordström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Nordström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
